--- a/Resources/Sheet/QS.xlsx
+++ b/Resources/Sheet/QS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\document\Thaiha\BoDoiApp\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED187177-FDF2-4FCD-8568-79F1E59B7C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342EADFD-0475-4F15-9DDC-32C8ABAF7E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{436C94DA-B63B-4AE7-8BA0-6B5AE70E1C41}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{436C94DA-B63B-4AE7-8BA0-6B5AE70E1C41}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -248,8 +248,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0"/>
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -467,15 +467,6 @@
   </cellStyleXfs>
   <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -509,9 +500,6 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -523,7 +511,7 @@
     <xf numFmtId="4" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -532,20 +520,44 @@
     <xf numFmtId="3" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="4" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="12" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -565,18 +577,6 @@
     <xf numFmtId="4" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -900,606 +900,606 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
+      <c r="A1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
     </row>
     <row r="3" spans="1:15" ht="16.5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="3" t="s">
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="3"/>
+      <c r="O3" s="34"/>
     </row>
     <row r="4" spans="1:15" ht="33">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="4" t="s">
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="33">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="4">
+      <c r="H5" s="33"/>
+      <c r="I5" s="1">
         <v>60</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="1">
         <v>82</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="1">
         <v>100</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="1">
         <v>12.7</v>
       </c>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15" ht="35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="4">
         <v>546</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="4">
         <v>22</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="4">
         <v>289</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="4">
         <v>27</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="4">
         <v>6</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="4">
         <v>54</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="4">
         <v>1444</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="4">
         <v>6</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="4">
         <v>4</v>
       </c>
-      <c r="K6" s="7">
-        <v>0</v>
-      </c>
-      <c r="L6" s="7">
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
         <v>3</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="4">
         <v>3</v>
       </c>
-      <c r="N6" s="7">
-        <v>0</v>
-      </c>
-      <c r="O6" s="7">
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="18.5">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="6">
         <v>546</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="6">
         <v>22</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="6">
         <v>289</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="6">
         <v>27</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="6">
         <v>6</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="6">
         <v>54</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="6">
         <v>1444</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="6">
         <v>6</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="6">
         <v>4</v>
       </c>
-      <c r="K7" s="9">
-        <v>0</v>
-      </c>
-      <c r="L7" s="9">
+      <c r="K7" s="6">
+        <v>0</v>
+      </c>
+      <c r="L7" s="6">
         <v>3</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="6">
         <v>3</v>
       </c>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-    </row>
-    <row r="8" spans="1:15" ht="52.5">
-      <c r="A8" s="7" t="s">
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" spans="1:15" ht="35">
+      <c r="A8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="4">
         <f>SUM(B9:B18)</f>
         <v>335</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="4">
         <f t="shared" ref="C8:O8" si="0">SUM(C9:C18)</f>
         <v>14</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="4">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="4">
         <f t="shared" si="0"/>
         <v>629</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="N8" s="7">
+      <c r="N8" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O8" s="7">
+      <c r="O8" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="54">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:15" ht="18.5">
+      <c r="A9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="6">
         <v>74</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="6">
         <v>4</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="6">
         <v>30</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9">
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6">
         <v>139</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9">
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6">
         <v>4</v>
       </c>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-    </row>
-    <row r="10" spans="1:15" ht="36">
-      <c r="A10" s="10" t="s">
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" ht="18.5">
+      <c r="A10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="6">
         <v>69</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="6">
         <v>4</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="6">
         <v>26</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9">
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6">
         <v>130</v>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9">
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6">
         <v>6</v>
       </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-    </row>
-    <row r="11" spans="1:15" ht="90">
-      <c r="A11" s="10" t="s">
+      <c r="M10" s="6"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" ht="36">
+      <c r="A11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="6">
         <v>82</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="6">
         <v>4</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="6">
         <v>26</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9">
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6">
         <v>156</v>
       </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9">
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6">
         <v>6</v>
       </c>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-    </row>
-    <row r="12" spans="1:15" ht="36">
-      <c r="A12" s="10" t="s">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" ht="18.5">
+      <c r="A12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="6">
         <v>28</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9">
+      <c r="C12" s="6"/>
+      <c r="D12" s="6">
         <v>10</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9">
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6">
         <v>56</v>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-    </row>
-    <row r="13" spans="1:15" ht="36">
-      <c r="A13" s="11" t="s">
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" ht="18.5">
+      <c r="A13" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="9">
         <v>3</v>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12">
-        <v>0</v>
-      </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12">
-        <v>0</v>
-      </c>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-    </row>
-    <row r="14" spans="1:15" ht="36">
-      <c r="A14" s="11" t="s">
+      <c r="C13" s="9"/>
+      <c r="D13" s="9">
+        <v>0</v>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9">
+        <v>0</v>
+      </c>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" ht="18.5">
+      <c r="A14" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="9">
         <v>9</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12">
+      <c r="C14" s="9"/>
+      <c r="D14" s="9">
         <v>2</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12">
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9">
         <v>8</v>
       </c>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-    </row>
-    <row r="15" spans="1:15" ht="36">
-      <c r="A15" s="11" t="s">
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" ht="18.5">
+      <c r="A15" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="9">
         <v>26</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="9">
         <v>2</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="9">
         <v>24</v>
       </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12">
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9">
         <v>52</v>
       </c>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
     </row>
     <row r="16" spans="1:15" ht="18.5">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="6">
         <v>32</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6">
         <v>22</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9">
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6">
         <v>64</v>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-    </row>
-    <row r="17" spans="1:15" ht="36">
-      <c r="A17" s="10" t="s">
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="1:15" ht="18.5">
+      <c r="A17" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="6">
         <v>3</v>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9">
+      <c r="C17" s="6"/>
+      <c r="D17" s="6">
         <v>1</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9">
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6">
         <v>6</v>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
     </row>
     <row r="18" spans="1:15" ht="18.5">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="6">
         <v>9</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6">
         <v>9</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9">
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6">
         <v>18</v>
       </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
     </row>
     <row r="19" spans="1:15" ht="17.5">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="11">
         <f t="shared" ref="B19:O19" si="1">B7+B8</f>
         <v>881</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="11">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="11">
         <f t="shared" si="1"/>
         <v>439</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="11">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="11">
         <f>G7+G8</f>
         <v>54</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="11">
         <f t="shared" si="1"/>
         <v>2073</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="11">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="11">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L19" s="14">
+      <c r="L19" s="11">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="M19" s="14">
+      <c r="M19" s="11">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="N19" s="14">
+      <c r="N19" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O19" s="14">
+      <c r="O19" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1531,294 +1531,294 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="19"/>
-      <c r="B1" s="20" t="s">
+      <c r="A1" s="15"/>
+      <c r="B1" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="17" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="25" t="e">
+      <c r="B2" s="21" t="e">
         <f>Sheet5!C19</f>
         <v>#REF!</v>
       </c>
-      <c r="C2" s="24">
+      <c r="C2" s="20">
         <v>1.4E-2</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="21">
         <v>24</v>
       </c>
-      <c r="E2" s="24" t="e">
+      <c r="E2" s="20" t="e">
         <f>B2*C2*D2/1000</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="25" t="e">
+      <c r="B3" s="21" t="e">
         <f>Sheet5!D19</f>
         <v>#REF!</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="20">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="21">
         <v>300</v>
       </c>
-      <c r="E3" s="24" t="e">
+      <c r="E3" s="20" t="e">
         <f>B3*C3*D3/1000</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="25" t="e">
+      <c r="B4" s="21" t="e">
         <f>Sheet5!E19</f>
         <v>#REF!</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="20">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="21">
         <v>600</v>
       </c>
-      <c r="E4" s="24" t="e">
+      <c r="E4" s="20" t="e">
         <f>B4*C4*D4/1000</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="25" t="e">
+      <c r="B5" s="21" t="e">
         <f>Sheet5!F19</f>
         <v>#REF!</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="20">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="21">
         <v>1200</v>
       </c>
-      <c r="E5" s="24" t="e">
+      <c r="E5" s="20" t="e">
         <f>B5*C5*D5/1000</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="25" t="e">
+      <c r="B6" s="21" t="e">
         <f>Sheet5!G19</f>
         <v>#REF!</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="20">
         <v>5.5</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="21">
         <v>12</v>
       </c>
-      <c r="E6" s="24" t="e">
+      <c r="E6" s="20" t="e">
         <f>B6*C6*D6/1000</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="17.5">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="27" t="e">
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="22" t="e">
         <f>SUM(E2:E6)</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="25" t="e">
+      <c r="B8" s="21" t="e">
         <f>Sheet5!I19</f>
         <v>#REF!</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="20">
         <v>2.1</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="21">
         <v>80</v>
       </c>
-      <c r="E8" s="24" t="e">
+      <c r="E8" s="20" t="e">
         <f>D8*C8*B8/1000</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="25" t="e">
+      <c r="B9" s="21" t="e">
         <f>Sheet5!J19</f>
         <v>#REF!</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="20">
         <v>5</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="21">
         <v>100</v>
       </c>
-      <c r="E9" s="24" t="e">
+      <c r="E9" s="20" t="e">
         <f>D9*C9*B9/1000</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="25" t="e">
+      <c r="B10" s="21" t="e">
         <f>Sheet5!K19</f>
         <v>#REF!</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="20">
         <v>23</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="21">
         <v>80</v>
       </c>
-      <c r="E10" s="24" t="e">
+      <c r="E10" s="20" t="e">
         <f>D10*C10*B10/1000</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="25" t="e">
+      <c r="B11" s="21" t="e">
         <f>Sheet5!L19</f>
         <v>#REF!</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="20">
         <v>16.5</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="21">
         <v>30</v>
       </c>
-      <c r="E11" s="24" t="e">
+      <c r="E11" s="20" t="e">
         <f>D11*C11*B11/1000</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="17.5">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="27" t="e">
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="22" t="e">
         <f>SUM(E8:E11)</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="25" t="e">
+      <c r="B13" s="21" t="e">
         <f>Sheet5!M19</f>
         <v>#REF!</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="20">
         <v>0.17</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="21">
         <v>1200</v>
       </c>
-      <c r="E13" s="24" t="e">
+      <c r="E13" s="20" t="e">
         <f>B13*C13*D13/1000</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="17.5">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="35" t="e">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="24" t="e">
         <f>E13</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="42" t="e">
+      <c r="B15" s="31" t="e">
         <f>Sheet5!H19</f>
         <v>#REF!</v>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="27">
         <v>0.75</v>
       </c>
-      <c r="D15" s="39"/>
-      <c r="E15" s="40" t="e">
+      <c r="D15" s="28"/>
+      <c r="E15" s="29" t="e">
         <f>C15*B15/1000</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="17.5">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="35" t="e">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="24" t="e">
         <f>E15</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="40">
+      <c r="B17" s="31"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="17.5">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35">
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="24">
         <v>0</v>
       </c>
     </row>
@@ -1846,564 +1846,564 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
     </row>
     <row r="3" spans="1:15" ht="17.5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="15" t="s">
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="15"/>
+      <c r="O3" s="35"/>
     </row>
     <row r="4" spans="1:15" ht="33">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="4" t="s">
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="33">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="4">
+      <c r="H5" s="33"/>
+      <c r="I5" s="1">
         <v>60</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="1">
         <v>82</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="1">
         <v>100</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="1">
         <v>12.7</v>
       </c>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-    </row>
-    <row r="6" spans="1:15" ht="70">
-      <c r="A6" s="7" t="s">
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" spans="1:15" ht="35">
+      <c r="A6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="4">
         <v>111</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="4">
         <v>4</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="4">
         <v>68</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="4">
         <v>9</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="4">
         <v>2</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="4">
         <v>18</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="4">
         <v>346</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="4">
         <f>I7</f>
         <v>2</v>
       </c>
-      <c r="J6" s="7">
-        <f t="shared" ref="J6:O6" si="0">J7</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="7">
+      <c r="J6" s="4">
+        <f t="shared" ref="J6:M6" si="0">J7</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="4">
         <f>L7</f>
         <v>0</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="4">
         <f>N7</f>
         <v>0</v>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="4">
         <f>O7</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="18.5">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="6">
         <v>111</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="6">
         <v>4</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="6">
         <v>68</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="6">
         <v>9</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="6">
         <v>2</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="6">
         <v>18</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="6">
         <v>346</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="6">
         <v>2</v>
       </c>
-      <c r="J7" s="9">
-        <v>0</v>
-      </c>
-      <c r="K7" s="9">
-        <v>0</v>
-      </c>
-      <c r="L7" s="9">
-        <v>0</v>
-      </c>
-      <c r="M7" s="9">
-        <v>0</v>
-      </c>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-    </row>
-    <row r="8" spans="1:15" ht="52.5">
-      <c r="A8" s="7" t="s">
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0</v>
+      </c>
+      <c r="L7" s="6">
+        <v>0</v>
+      </c>
+      <c r="M7" s="6">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" spans="1:15" ht="35">
+      <c r="A8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="7">
-        <f t="shared" ref="B8:O8" si="1">SUM(B9:B16)</f>
+      <c r="B8" s="4">
+        <f t="shared" ref="B8:N8" si="1">SUM(B9:B16)</f>
         <v>200</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="4">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="4">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="4">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="4">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="4">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="4">
         <f t="shared" si="1"/>
         <v>476</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="4">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="4">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="4">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="4">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="N8" s="7">
+      <c r="N8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O8" s="7">
+      <c r="O8" s="4">
         <f>SUM(O9:O16)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="54">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:15" ht="18.5">
+      <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="6">
         <v>29</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6">
         <v>11</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9">
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6">
         <v>58</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9">
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6">
         <v>3</v>
       </c>
-      <c r="M9" s="9"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-    </row>
-    <row r="10" spans="1:15" ht="36">
-      <c r="A10" s="10" t="s">
+      <c r="M9" s="6"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" ht="18.5">
+      <c r="A10" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="6">
         <v>34</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="6">
         <v>4</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="6">
         <v>12</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9">
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6">
         <v>62</v>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9">
+      <c r="I10" s="6"/>
+      <c r="J10" s="6">
         <v>3</v>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-    </row>
-    <row r="11" spans="1:15" ht="72">
-      <c r="A11" s="10" t="s">
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" ht="36">
+      <c r="A11" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="6">
         <v>35</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9">
+      <c r="C11" s="6"/>
+      <c r="D11" s="6">
         <v>11</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9">
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6">
         <v>70</v>
       </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9">
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6">
         <v>3</v>
       </c>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-    </row>
-    <row r="12" spans="1:15" ht="36">
-      <c r="A12" s="10" t="s">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" ht="18.5">
+      <c r="A12" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="6">
         <v>82</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="6">
         <v>4</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="6">
         <v>48</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="6">
         <v>6</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="6">
         <v>2</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="6">
         <v>12</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="6">
         <f>346-102</f>
         <v>244</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="6">
         <v>2</v>
       </c>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
     </row>
     <row r="13" spans="1:15" ht="18.5">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="9">
         <v>1</v>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-    </row>
-    <row r="14" spans="1:15" ht="72">
-      <c r="A14" s="11" t="s">
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" ht="36">
+      <c r="A14" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="9">
         <v>5</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12">
+      <c r="C14" s="9"/>
+      <c r="D14" s="9">
         <v>2</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12">
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9">
         <v>12</v>
       </c>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-    </row>
-    <row r="15" spans="1:15" ht="90">
-      <c r="A15" s="11" t="s">
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" ht="36">
+      <c r="A15" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="9">
         <v>5</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12">
+      <c r="C15" s="9"/>
+      <c r="D15" s="9">
         <v>2</v>
       </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12">
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9">
         <v>12</v>
       </c>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
     </row>
     <row r="16" spans="1:15" ht="18.5">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="6">
         <v>9</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6">
         <v>3</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9">
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6">
         <v>18</v>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
     </row>
     <row r="17" spans="1:15" ht="17.5">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="11">
         <f t="shared" ref="B17:O17" si="2">B7+B8</f>
         <v>311</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="11">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="11">
         <f t="shared" si="2"/>
         <v>157</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="11">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="11">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="11">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="11">
         <f t="shared" si="2"/>
         <v>822</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="11">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="11">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L17" s="14">
+      <c r="L17" s="11">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="M17" s="14">
+      <c r="M17" s="11">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="N17" s="14">
+      <c r="N17" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O17" s="14">
+      <c r="O17" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2434,405 +2434,405 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
     </row>
     <row r="3" spans="1:15" ht="17.5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="15" t="s">
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="15"/>
+      <c r="O3" s="35"/>
     </row>
     <row r="4" spans="1:15" ht="33">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="4" t="s">
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="33">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="4">
+      <c r="H5" s="33"/>
+      <c r="I5" s="1">
         <v>60</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="1">
         <v>82</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="1">
         <v>100</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="1">
         <v>12.7</v>
       </c>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-    </row>
-    <row r="6" spans="1:15" ht="70">
-      <c r="A6" s="7" t="s">
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" spans="1:15" ht="35">
+      <c r="A6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="4">
         <v>111</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="4">
         <v>4</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="4">
         <v>68</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="4">
         <v>9</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="4">
         <v>2</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="4">
         <v>18</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="4">
         <v>346</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="4">
         <f>I7</f>
         <v>2</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="4">
         <f t="shared" ref="J6:O6" si="0">J7</f>
         <v>0</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="18.5">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="6">
         <v>111</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="6">
         <v>4</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="6">
         <v>68</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="6">
         <v>9</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="6">
         <v>2</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="6">
         <v>18</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="6">
         <v>346</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="6">
         <v>2</v>
       </c>
-      <c r="J7" s="9">
-        <v>0</v>
-      </c>
-      <c r="K7" s="9">
-        <v>0</v>
-      </c>
-      <c r="L7" s="9">
-        <v>0</v>
-      </c>
-      <c r="M7" s="9">
-        <v>0</v>
-      </c>
-      <c r="N7" s="6">
-        <v>0</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="52.5">
-      <c r="A8" s="7" t="s">
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0</v>
+      </c>
+      <c r="L7" s="6">
+        <v>0</v>
+      </c>
+      <c r="M7" s="6">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="35">
+      <c r="A8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="4">
         <f>SUM(B9:B10)</f>
         <v>22</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="4">
         <f t="shared" ref="C8:O8" si="1">SUM(C9:C10)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="4">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="4">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="4">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N8" s="7">
+      <c r="N8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O8" s="7">
+      <c r="O8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="54">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:15" ht="18.5">
+      <c r="A9" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="6">
         <v>17</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6">
         <v>5</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9">
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6">
         <v>32</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9">
+      <c r="I9" s="6"/>
+      <c r="J9" s="6">
         <v>1</v>
       </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
     </row>
     <row r="10" spans="1:15" ht="18">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="13">
         <v>5</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17">
+      <c r="C10" s="13"/>
+      <c r="D10" s="13">
         <v>2</v>
       </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17">
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13">
         <v>12</v>
       </c>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
     </row>
     <row r="11" spans="1:15" ht="17.5">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="11">
         <f t="shared" ref="B11:O11" si="2">B7+B8</f>
         <v>133</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="11">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="11">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="11">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="11">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="11">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="11">
         <f t="shared" si="2"/>
         <v>390</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="11">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L11" s="14">
+      <c r="L11" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M11" s="14">
+      <c r="M11" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N11" s="14">
+      <c r="N11" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O11" s="14">
+      <c r="O11" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2864,374 +2864,374 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
     </row>
     <row r="3" spans="1:15" ht="17.5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="15" t="s">
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="15"/>
+      <c r="O3" s="35"/>
     </row>
     <row r="4" spans="1:15" ht="33">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="4" t="s">
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="33">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="4">
+      <c r="H5" s="33"/>
+      <c r="I5" s="1">
         <v>60</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="1">
         <v>82</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="1">
         <v>100</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="1">
         <v>12.7</v>
       </c>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-    </row>
-    <row r="6" spans="1:15" ht="70">
-      <c r="A6" s="7" t="s">
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" spans="1:15" ht="35">
+      <c r="A6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="4">
         <f>B7</f>
         <v>29</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="4">
         <f t="shared" ref="C6:O6" si="0">C7</f>
         <v>0</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="4">
         <f t="shared" si="0"/>
         <v>102</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="18.5">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="6">
         <v>29</v>
       </c>
-      <c r="C7" s="9">
-        <v>0</v>
-      </c>
-      <c r="D7" s="9">
+      <c r="C7" s="6">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6">
         <v>20</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="6">
         <v>3</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9">
+      <c r="F7" s="6"/>
+      <c r="G7" s="6">
         <v>6</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="6">
         <v>102</v>
       </c>
-      <c r="I7" s="9">
-        <v>0</v>
-      </c>
-      <c r="J7" s="9">
-        <v>0</v>
-      </c>
-      <c r="K7" s="9">
-        <v>0</v>
-      </c>
-      <c r="L7" s="9">
-        <v>0</v>
-      </c>
-      <c r="M7" s="9">
-        <v>0</v>
-      </c>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-    </row>
-    <row r="8" spans="1:15" ht="52.5">
-      <c r="A8" s="7" t="s">
+      <c r="I7" s="6">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0</v>
+      </c>
+      <c r="L7" s="6">
+        <v>0</v>
+      </c>
+      <c r="M7" s="6">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" spans="1:15" ht="35">
+      <c r="A8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="4">
         <f t="shared" ref="B8:I8" si="1">SUM(B9:B9)</f>
         <v>1</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J8" s="7">
-        <v>0</v>
-      </c>
-      <c r="K8" s="7">
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
         <f>SUM(K9:K9)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="4">
         <f>SUM(L9:L9)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="4">
         <f>SUM(M9:M9)</f>
         <v>0</v>
       </c>
-      <c r="N8" s="7">
+      <c r="N8" s="4">
         <f>SUM(N9:N9)</f>
         <v>0</v>
       </c>
-      <c r="O8" s="7">
+      <c r="O8" s="4">
         <f>SUM(O9:O9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="72">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:15" ht="36">
+      <c r="A9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="6">
         <v>1</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
     </row>
     <row r="10" spans="1:15" ht="17.5">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="11">
         <f>B8+B6</f>
         <v>30</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="11">
         <f t="shared" ref="C10:O10" si="2">C8+C6</f>
         <v>0</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="11">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="11">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="11">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="11">
         <f t="shared" si="2"/>
         <v>102</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L10" s="14">
+      <c r="L10" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M10" s="14">
+      <c r="M10" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N10" s="14">
+      <c r="N10" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O10" s="14">
+      <c r="O10" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3263,638 +3263,638 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
     </row>
     <row r="3" spans="1:15" ht="17.5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="15" t="s">
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="15"/>
+      <c r="O3" s="35"/>
     </row>
     <row r="4" spans="1:15" ht="33">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="4" t="s">
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="33">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="4">
+      <c r="H5" s="33"/>
+      <c r="I5" s="1">
         <v>60</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="1">
         <v>82</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="1">
         <v>100</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="1">
         <v>12.7</v>
       </c>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-    </row>
-    <row r="6" spans="1:15" ht="70">
-      <c r="A6" s="7" t="s">
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" spans="1:15" ht="35">
+      <c r="A6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="7" t="e">
+      <c r="B6" s="4" t="e">
         <f>B7</f>
         <v>#REF!</v>
       </c>
-      <c r="C6" s="7" t="e">
+      <c r="C6" s="4" t="e">
         <f>C7</f>
         <v>#REF!</v>
       </c>
-      <c r="D6" s="7" t="e">
-        <f t="shared" ref="C6:O6" si="0">D7</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E6" s="7" t="e">
+      <c r="D6" s="4" t="e">
+        <f t="shared" ref="D6:O6" si="0">D7</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E6" s="4" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="F6" s="7" t="e">
+      <c r="F6" s="4" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="G6" s="7" t="e">
+      <c r="G6" s="4" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="H6" s="7" t="e">
+      <c r="H6" s="4" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="I6" s="7" t="e">
+      <c r="I6" s="4" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="J6" s="7" t="e">
+      <c r="J6" s="4" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="K6" s="7" t="e">
+      <c r="K6" s="4" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="L6" s="7" t="e">
+      <c r="L6" s="4" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="M6" s="7" t="e">
+      <c r="M6" s="4" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="N6" s="7" t="e">
+      <c r="N6" s="4" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="O6" s="7" t="e">
+      <c r="O6" s="4" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="52.5">
-      <c r="A7" s="18" t="s">
+    <row r="7" spans="1:15" ht="35">
+      <c r="A7" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="18" t="e">
+      <c r="B7" s="14" t="e">
         <f>#REF!-#REF!-#REF!-#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="C7" s="18" t="e">
-        <f t="shared" ref="C7:O7" si="1">#REF!-#REF!-#REF!-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D7" s="18" t="e">
-        <f t="shared" ref="D7:O7" si="2">#REF!-#REF!-#REF!-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E7" s="18" t="e">
-        <f t="shared" ref="E7:O7" si="3">#REF!-#REF!-#REF!-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F7" s="18" t="e">
-        <f t="shared" ref="F7:O7" si="4">#REF!-#REF!-#REF!-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G7" s="18" t="e">
-        <f t="shared" ref="G7:O7" si="5">#REF!-#REF!-#REF!-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H7" s="18" t="e">
-        <f t="shared" ref="H7:O7" si="6">#REF!-#REF!-#REF!-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I7" s="18" t="e">
-        <f t="shared" ref="I7:O7" si="7">#REF!-#REF!-#REF!-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J7" s="18" t="e">
-        <f t="shared" ref="J7:O7" si="8">#REF!-#REF!-#REF!-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K7" s="18" t="e">
-        <f t="shared" ref="K7:O7" si="9">#REF!-#REF!-#REF!-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L7" s="18" t="e">
-        <f t="shared" ref="L7:O7" si="10">#REF!-#REF!-#REF!-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M7" s="18" t="e">
-        <f t="shared" ref="M7:O7" si="11">#REF!-#REF!-#REF!-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N7" s="18" t="e">
-        <f t="shared" ref="N7:O7" si="12">#REF!-#REF!-#REF!-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O7" s="18" t="e">
+      <c r="C7" s="14" t="e">
+        <f t="shared" ref="C7" si="1">#REF!-#REF!-#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D7" s="14" t="e">
+        <f t="shared" ref="D7" si="2">#REF!-#REF!-#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E7" s="14" t="e">
+        <f t="shared" ref="E7" si="3">#REF!-#REF!-#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F7" s="14" t="e">
+        <f t="shared" ref="F7" si="4">#REF!-#REF!-#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="G7" s="14" t="e">
+        <f t="shared" ref="G7" si="5">#REF!-#REF!-#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H7" s="14" t="e">
+        <f t="shared" ref="H7" si="6">#REF!-#REF!-#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I7" s="14" t="e">
+        <f t="shared" ref="I7" si="7">#REF!-#REF!-#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J7" s="14" t="e">
+        <f t="shared" ref="J7" si="8">#REF!-#REF!-#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K7" s="14" t="e">
+        <f t="shared" ref="K7" si="9">#REF!-#REF!-#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L7" s="14" t="e">
+        <f t="shared" ref="L7" si="10">#REF!-#REF!-#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M7" s="14" t="e">
+        <f t="shared" ref="M7" si="11">#REF!-#REF!-#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="N7" s="14" t="e">
+        <f t="shared" ref="N7" si="12">#REF!-#REF!-#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="O7" s="14" t="e">
         <f t="shared" ref="O7" si="13">#REF!-#REF!-#REF!-#REF!</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="70">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:15" ht="52.5">
+      <c r="A8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="4">
         <f>SUM(B9:B18)</f>
         <v>335</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="4">
         <f t="shared" ref="C8:O8" si="14">SUM(C9:C18)</f>
         <v>14</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="4">
         <f t="shared" si="14"/>
         <v>150</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="4">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="4">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="4">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="4">
         <f t="shared" si="14"/>
         <v>629</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="4">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="4">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="4">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="4">
         <f t="shared" si="14"/>
         <v>6</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="4">
         <f t="shared" si="14"/>
         <v>6</v>
       </c>
-      <c r="N8" s="7">
+      <c r="N8" s="4">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="O8" s="7">
+      <c r="O8" s="4">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="54">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:15" ht="18.5">
+      <c r="A9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="6">
         <v>74</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="6">
         <v>4</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="6">
         <v>30</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9">
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6">
         <v>139</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9">
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6">
         <v>4</v>
       </c>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-    </row>
-    <row r="10" spans="1:15" ht="36">
-      <c r="A10" s="10" t="s">
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" ht="18.5">
+      <c r="A10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="6">
         <v>69</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="6">
         <v>4</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="6">
         <v>26</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9">
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6">
         <v>130</v>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9">
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6">
         <v>6</v>
       </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-    </row>
-    <row r="11" spans="1:15" ht="90">
-      <c r="A11" s="10" t="s">
+      <c r="M10" s="6"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" ht="36">
+      <c r="A11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="6">
         <v>82</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="6">
         <v>4</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="6">
         <v>26</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9">
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6">
         <v>156</v>
       </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9">
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6">
         <v>6</v>
       </c>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-    </row>
-    <row r="12" spans="1:15" ht="36">
-      <c r="A12" s="10" t="s">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" ht="18.5">
+      <c r="A12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="6">
         <v>28</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9">
+      <c r="C12" s="6"/>
+      <c r="D12" s="6">
         <v>10</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9">
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6">
         <v>56</v>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-    </row>
-    <row r="13" spans="1:15" ht="36">
-      <c r="A13" s="11" t="s">
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" ht="18.5">
+      <c r="A13" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="9">
         <v>3</v>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12">
-        <v>0</v>
-      </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12">
-        <v>0</v>
-      </c>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-    </row>
-    <row r="14" spans="1:15" ht="36">
-      <c r="A14" s="11" t="s">
+      <c r="C13" s="9"/>
+      <c r="D13" s="9">
+        <v>0</v>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9">
+        <v>0</v>
+      </c>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" ht="18.5">
+      <c r="A14" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="9">
         <v>9</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12">
+      <c r="C14" s="9"/>
+      <c r="D14" s="9">
         <v>2</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12">
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9">
         <v>8</v>
       </c>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-    </row>
-    <row r="15" spans="1:15" ht="36">
-      <c r="A15" s="11" t="s">
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" ht="18.5">
+      <c r="A15" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="9">
         <v>26</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="9">
         <v>2</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="9">
         <v>24</v>
       </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12">
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9">
         <v>52</v>
       </c>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
     </row>
     <row r="16" spans="1:15" ht="18.5">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="6">
         <v>32</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6">
         <v>22</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9">
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6">
         <v>64</v>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-    </row>
-    <row r="17" spans="1:15" ht="36">
-      <c r="A17" s="10" t="s">
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="1:15" ht="18.5">
+      <c r="A17" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="6">
         <v>3</v>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9">
+      <c r="C17" s="6"/>
+      <c r="D17" s="6">
         <v>1</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9">
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6">
         <v>6</v>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
     </row>
     <row r="18" spans="1:15" ht="18.5">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="6">
         <v>9</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6">
         <v>9</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9">
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6">
         <v>18</v>
       </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
     </row>
     <row r="19" spans="1:15" ht="17.5">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="14" t="e">
+      <c r="B19" s="11" t="e">
         <f>B7+B8</f>
         <v>#REF!</v>
       </c>
-      <c r="C19" s="14" t="e">
-        <f t="shared" ref="B19:O19" si="15">C7+C8</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D19" s="14" t="e">
+      <c r="C19" s="11" t="e">
+        <f t="shared" ref="C19:O19" si="15">C7+C8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D19" s="11" t="e">
         <f t="shared" si="15"/>
         <v>#REF!</v>
       </c>
-      <c r="E19" s="14" t="e">
+      <c r="E19" s="11" t="e">
         <f t="shared" si="15"/>
         <v>#REF!</v>
       </c>
-      <c r="F19" s="14" t="e">
+      <c r="F19" s="11" t="e">
         <f t="shared" si="15"/>
         <v>#REF!</v>
       </c>
-      <c r="G19" s="14" t="e">
+      <c r="G19" s="11" t="e">
         <f t="shared" si="15"/>
         <v>#REF!</v>
       </c>
-      <c r="H19" s="14" t="e">
+      <c r="H19" s="11" t="e">
         <f>H7+H8</f>
         <v>#REF!</v>
       </c>
-      <c r="I19" s="14" t="e">
+      <c r="I19" s="11" t="e">
         <f t="shared" si="15"/>
         <v>#REF!</v>
       </c>
-      <c r="J19" s="14" t="e">
+      <c r="J19" s="11" t="e">
         <f t="shared" si="15"/>
         <v>#REF!</v>
       </c>
-      <c r="K19" s="14" t="e">
+      <c r="K19" s="11" t="e">
         <f t="shared" si="15"/>
         <v>#REF!</v>
       </c>
-      <c r="L19" s="14" t="e">
+      <c r="L19" s="11" t="e">
         <f t="shared" si="15"/>
         <v>#REF!</v>
       </c>
-      <c r="M19" s="14" t="e">
+      <c r="M19" s="11" t="e">
         <f t="shared" si="15"/>
         <v>#REF!</v>
       </c>
-      <c r="N19" s="14" t="e">
+      <c r="N19" s="11" t="e">
         <f t="shared" si="15"/>
         <v>#REF!</v>
       </c>
-      <c r="O19" s="14" t="e">
+      <c r="O19" s="11" t="e">
         <f t="shared" si="15"/>
         <v>#REF!</v>
       </c>
@@ -3920,299 +3920,300 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="13.90625" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" customWidth="1"/>
+    <col min="3" max="3" width="10.36328125" customWidth="1"/>
     <col min="5" max="5" width="12.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="19"/>
-      <c r="B1" s="20" t="s">
+      <c r="A1" s="15"/>
+      <c r="B1" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="17" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="23">
+      <c r="B2" s="19">
         <f>Sheet1!C19</f>
         <v>36</v>
       </c>
-      <c r="C2" s="24">
+      <c r="C2" s="20">
         <v>1.4E-2</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="21">
         <v>24</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="20">
         <f>B2*C2*D2/1000</f>
         <v>1.2096000000000001E-2</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="19">
         <f>Sheet1!D19</f>
         <v>439</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="20">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="21">
         <v>300</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="20">
         <f t="shared" ref="E3:E6" si="0">B3*C3*D3/1000</f>
         <v>2.8973999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="23">
+      <c r="B4" s="19">
         <f>Sheet1!E19</f>
         <v>27</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="20">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="21">
         <v>600</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="20">
         <f t="shared" si="0"/>
         <v>0.35639999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="19">
         <f>Sheet1!F19</f>
         <v>6</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="20">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="21">
         <v>1200</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="20">
         <f t="shared" si="0"/>
         <v>0.23760000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="19">
         <f>Sheet1!G19</f>
         <v>54</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="20">
         <v>5.5</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="21">
         <v>12</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="20">
         <f t="shared" si="0"/>
         <v>3.5640000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="17.5">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="27">
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="22">
         <f>SUM(E2:E6)</f>
         <v>7.0674960000000002</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="19">
         <f>Sheet1!I19</f>
         <v>6</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="23">
         <v>2.1</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="21">
         <v>80</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="20">
         <f>D8*C8*B8/1000</f>
         <v>1.008</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="19">
         <f>Sheet1!J19</f>
         <v>4</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="23">
         <v>5</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="21">
         <v>100</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="20">
         <f t="shared" ref="E9:E11" si="1">D9*C9*B9/1000</f>
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="19">
         <f>Sheet1!K19</f>
         <v>4</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="23">
         <v>23</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="21">
         <v>80</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="20">
         <f t="shared" si="1"/>
         <v>7.36</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="19">
         <f>Sheet1!L19</f>
         <v>9</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="23">
         <v>16.5</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="21">
         <v>30</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="20">
         <f t="shared" si="1"/>
         <v>4.4550000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="17.5">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="27">
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="22">
         <f>SUM(E8:E11)</f>
         <v>14.823</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B13" s="19">
         <f>Sheet1!M19</f>
         <v>9</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="20">
         <v>0.17</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="21">
         <v>1200</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="20">
         <f>B13*C13*D13/1000</f>
         <v>1.8360000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="17.5">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="35">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="24">
         <f>E13</f>
         <v>1.8360000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="26">
         <f>Sheet1!H19</f>
         <v>2073</v>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="27">
         <v>0.75</v>
       </c>
-      <c r="D15" s="39"/>
-      <c r="E15" s="40">
+      <c r="D15" s="28"/>
+      <c r="E15" s="29">
         <f>C15*B15/1000</f>
         <v>1.5547500000000001</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="17.5">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="35">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="24">
         <f>E15</f>
         <v>1.5547500000000001</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="40">
+      <c r="B17" s="26"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="17.5">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35">
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="24">
         <v>0</v>
       </c>
     </row>
@@ -4240,294 +4241,294 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="19"/>
-      <c r="B1" s="20" t="s">
+      <c r="A1" s="15"/>
+      <c r="B1" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="17" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="21">
         <f>Sheet2!C17</f>
         <v>12</v>
       </c>
-      <c r="C2" s="24">
+      <c r="C2" s="20">
         <v>1.4E-2</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="21">
         <v>24</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="20">
         <f>B2*C2*D2/1000</f>
         <v>4.032E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="21">
         <f>Sheet2!D17</f>
         <v>157</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="20">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="21">
         <v>300</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="20">
         <f>B3*C3*D3/1000</f>
         <v>1.0361999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="21">
         <f>Sheet2!E17</f>
         <v>15</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="20">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="21">
         <v>600</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="20">
         <f>B4*C4*D4/1000</f>
         <v>0.19799999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="21">
         <f>Sheet2!F17</f>
         <v>4</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="20">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="21">
         <v>1200</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="20">
         <f>B5*C5*D5/1000</f>
         <v>0.15840000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="21">
         <f>Sheet2!G17</f>
         <v>30</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="20">
         <v>5.5</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="21">
         <v>12</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="20">
         <f>B6*C6*D6/1000</f>
         <v>1.98</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="17.5">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="27">
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="22">
         <f>SUM(E2:E6)</f>
         <v>3.3766319999999999</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="21">
         <f>Sheet2!I17</f>
         <v>4</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="20">
         <v>2.1</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="21">
         <v>80</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="20">
         <f>D8*C8*B8/1000</f>
         <v>0.67200000000000004</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="21">
         <f>Sheet2!J17</f>
         <v>3</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="20">
         <v>5</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="21">
         <v>100</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="20">
         <f>D9*C9*B9/1000</f>
         <v>1.5</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="21">
         <f>Sheet2!K17</f>
         <v>0</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="20">
         <v>23</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="21">
         <v>80</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="20">
         <f>D10*C10*B10/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="21">
         <f>Sheet2!L17</f>
         <v>3</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="20">
         <v>16.5</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="21">
         <v>30</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="20">
         <f>D11*C11*B11/1000</f>
         <v>1.4850000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="17.5">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="27">
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="22">
         <f>SUM(E8:E11)</f>
         <v>3.657</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="21">
         <f>Sheet2!M17</f>
         <v>3</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="20">
         <v>0.17</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="21">
         <v>1200</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="20">
         <f>B13*C13*D13/1000</f>
         <v>0.61199999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="17.5">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="35">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="24">
         <f>E13</f>
         <v>0.61199999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="42">
+      <c r="B15" s="31">
         <f>Sheet2!H17</f>
         <v>822</v>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="27">
         <v>0.75</v>
       </c>
-      <c r="D15" s="39"/>
-      <c r="E15" s="40">
+      <c r="D15" s="28"/>
+      <c r="E15" s="29">
         <f>C15*B15/1000</f>
         <v>0.61650000000000005</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="17.5">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="35">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="24">
         <f>E15</f>
         <v>0.61650000000000005</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="40">
+      <c r="B17" s="31"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="17.5">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35">
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="24">
         <v>0</v>
       </c>
     </row>
@@ -4555,294 +4556,294 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="19"/>
-      <c r="B1" s="20" t="s">
+      <c r="A1" s="15"/>
+      <c r="B1" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="17" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="21">
         <f>Sheet3!C11</f>
         <v>4</v>
       </c>
-      <c r="C2" s="24">
+      <c r="C2" s="20">
         <v>1.4E-2</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="21">
         <v>24</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="20">
         <f>B2*C2*D2/1000</f>
         <v>1.3440000000000001E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="21">
         <f>Sheet3!D11</f>
         <v>75</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="20">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="21">
         <v>300</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="20">
         <f>B3*C3*D3/1000</f>
         <v>0.495</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="21">
         <f>Sheet3!E11</f>
         <v>9</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="20">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="21">
         <v>600</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="20">
         <f>B4*C4*D4/1000</f>
         <v>0.11879999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="21">
         <f>Sheet3!F11</f>
         <v>2</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="20">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="21">
         <v>1200</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="20">
         <f>B5*C5*D5/1000</f>
         <v>7.9200000000000007E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="21">
         <f>Sheet3!G11</f>
         <v>18</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="20">
         <v>5.5</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="21">
         <v>12</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="20">
         <f>B6*C6*D6/1000</f>
         <v>1.1879999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="17.5">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="27">
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="22">
         <f>SUM(E2:E6)</f>
         <v>1.882344</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="21">
         <f>Sheet3!I11</f>
         <v>2</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="20">
         <v>2.1</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="21">
         <v>80</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="20">
         <f>D8*C8*B8/1000</f>
         <v>0.33600000000000002</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="21">
         <f>Sheet3!J11</f>
         <v>1</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="20">
         <v>5</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="21">
         <v>100</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="20">
         <f>D9*C9*B9/1000</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="21">
         <f>Sheet3!K11</f>
         <v>0</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="20">
         <v>23</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="21">
         <v>80</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="20">
         <f>D10*C10*B10/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="21">
         <f>Sheet3!L11</f>
         <v>0</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="20">
         <v>16.5</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="21">
         <v>30</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="20">
         <f>D11*C11*B11/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="17.5">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="27">
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="22">
         <f>SUM(E8:E11)</f>
         <v>0.83600000000000008</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="21">
         <f>Sheet3!M11</f>
         <v>0</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="20">
         <v>0.17</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="21">
         <v>1200</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="20">
         <f>B13*C13*D13/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="17.5">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="35">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="24">
         <f>E13</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="42">
+      <c r="B15" s="31">
         <f>Sheet3!H11</f>
         <v>390</v>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="27">
         <v>0.75</v>
       </c>
-      <c r="D15" s="39"/>
-      <c r="E15" s="40">
+      <c r="D15" s="28"/>
+      <c r="E15" s="29">
         <f>C15*B15/1000</f>
         <v>0.29249999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="17.5">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="35">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="24">
         <f>E15</f>
         <v>0.29249999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="40">
+      <c r="B17" s="31"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="17.5">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35">
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="24">
         <v>0</v>
       </c>
     </row>
@@ -4871,294 +4872,294 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="19"/>
-      <c r="B1" s="20" t="s">
+      <c r="A1" s="15"/>
+      <c r="B1" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="17" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="21">
         <f>Sheet4!C10</f>
         <v>0</v>
       </c>
-      <c r="C2" s="24">
+      <c r="C2" s="20">
         <v>1.4E-2</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="21">
         <v>24</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="20">
         <f>B2*C2*D2/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="21">
         <f>Sheet4!D10</f>
         <v>20</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="20">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="21">
         <v>300</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="20">
         <f>B3*C3*D3/1000</f>
         <v>0.13199999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="21">
         <f>Sheet4!E10</f>
         <v>3</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="20">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="21">
         <v>600</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="20">
         <f>B4*C4*D4/1000</f>
         <v>3.9600000000000003E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="21">
         <f>Sheet4!F10</f>
         <v>0</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="20">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="21">
         <v>1200</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="20">
         <f>B5*C5*D5/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="21">
         <f>Sheet4!G10</f>
         <v>6</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="20">
         <v>5.5</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="21">
         <v>12</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="20">
         <f>B6*C6*D6/1000</f>
         <v>0.39600000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="17.5">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="27">
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="22">
         <f>SUM(E2:E6)</f>
         <v>0.56759999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="21">
         <f>Sheet4!I10</f>
         <v>0</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="20">
         <v>2.1</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="21">
         <v>80</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="20">
         <f>D8*C8*B8/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="21">
         <f>Sheet4!J10</f>
         <v>0</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="20">
         <v>5</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="21">
         <v>100</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="20">
         <f>D9*C9*B9/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="21">
         <f>Sheet4!K10</f>
         <v>0</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="20">
         <v>23</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="21">
         <v>80</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="20">
         <f>D10*C10*B10/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="21">
         <f>Sheet4!L10</f>
         <v>0</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="20">
         <v>16.5</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="21">
         <v>30</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="20">
         <f>D11*C11*B11/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="17.5">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="27">
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="22">
         <f>SUM(E8:E11)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="21">
         <f>Sheet4!M10</f>
         <v>0</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="20">
         <v>0.17</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="21">
         <v>1200</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="20">
         <f>B13*C13*D13/1000</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="17.5">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="35">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="24">
         <f>E13</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="42">
+      <c r="B15" s="31">
         <f>Sheet4!H10</f>
         <v>102</v>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="27">
         <v>0.75</v>
       </c>
-      <c r="D15" s="39"/>
-      <c r="E15" s="40">
+      <c r="D15" s="28"/>
+      <c r="E15" s="29">
         <f>C15*B15/1000</f>
         <v>7.6499999999999999E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="17.5">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="35">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="24">
         <f>E15</f>
         <v>7.6499999999999999E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="40">
+      <c r="B17" s="31"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="17.5">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35">
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="24">
         <v>0</v>
       </c>
     </row>

--- a/Resources/Sheet/QS.xlsx
+++ b/Resources/Sheet/QS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\document\Thaiha\BoDoiApp\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342EADFD-0475-4F15-9DDC-32C8ABAF7E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5687DDC8-CFFC-4FB3-8B5E-934C82CF05C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{436C94DA-B63B-4AE7-8BA0-6B5AE70E1C41}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="5" xr2:uid="{436C94DA-B63B-4AE7-8BA0-6B5AE70E1C41}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,16 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
-    <sheet name="DAN1" sheetId="6" r:id="rId6"/>
-    <sheet name="DAN2" sheetId="7" r:id="rId7"/>
-    <sheet name="DAN3" sheetId="8" r:id="rId8"/>
-    <sheet name="DAN4" sheetId="9" r:id="rId9"/>
-    <sheet name="DAN5" sheetId="10" r:id="rId10"/>
+    <sheet name="Sheet6" sheetId="11" r:id="rId6"/>
+    <sheet name="DAN1" sheetId="6" r:id="rId7"/>
+    <sheet name="DAN2" sheetId="7" r:id="rId8"/>
+    <sheet name="DAN3" sheetId="8" r:id="rId9"/>
+    <sheet name="DAN4" sheetId="9" r:id="rId10"/>
+    <sheet name="DAN5" sheetId="10" r:id="rId11"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId12"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="99">
   <si>
     <t>TỔ CHỨC BIÊN CHẾ, TRANG BỊ TIỂU ĐOÀN BỘ BINH TIẾN CÔNG RỪNG NÚI</t>
   </si>
@@ -241,6 +245,96 @@
   </si>
   <si>
     <t>1 CS Thuốc nổ</t>
+  </si>
+  <si>
+    <t>Loại đạn</t>
+  </si>
+  <si>
+    <t>Số lượng VK</t>
+  </si>
+  <si>
+    <t>Nhu cầu</t>
+  </si>
+  <si>
+    <t>Tiêu thụ</t>
+  </si>
+  <si>
+    <t>PC SCĐ</t>
+  </si>
+  <si>
+    <t>Hiện có</t>
+  </si>
+  <si>
+    <t>PC TNS</t>
+  </si>
+  <si>
+    <t>Kế hoạch tiếp nhận, bảo đảm</t>
+  </si>
+  <si>
+    <t>GĐCB</t>
+  </si>
+  <si>
+    <t>GĐCĐ</t>
+  </si>
+  <si>
+    <t>ĐV</t>
+  </si>
+  <si>
+    <t>Kho</t>
+  </si>
+  <si>
+    <t>Trước nổ súng</t>
+  </si>
+  <si>
+    <t>thực hành nổ súng</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>Cơ số</t>
+  </si>
+  <si>
+    <t>Toàn d</t>
+  </si>
+  <si>
+    <t>SMPK 12,7mm</t>
+  </si>
+  <si>
+    <t>Đạn BB nhóm 2</t>
+  </si>
+  <si>
+    <t>Cối 100mm</t>
+  </si>
+  <si>
+    <t>Cối 82mm</t>
+  </si>
+  <si>
+    <t>Cối 60mm</t>
+  </si>
+  <si>
+    <t>Súng SPG-9</t>
+  </si>
+  <si>
+    <t>Đạn BB nhóm 1</t>
+  </si>
+  <si>
+    <t>Súng B41</t>
+  </si>
+  <si>
+    <t>Súng đại liên</t>
+  </si>
+  <si>
+    <t>Súng trung liên</t>
+  </si>
+  <si>
+    <t>Súng tiểu liên</t>
+  </si>
+  <si>
+    <t>Súng ngắn</t>
   </si>
 </sst>
 </file>
@@ -251,7 +345,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -362,8 +456,21 @@
       <family val="1"/>
       <charset val="163"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -397,6 +504,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -465,7 +584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -577,6 +696,54 @@
     <xf numFmtId="4" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -592,6 +759,108 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Giao diện"/>
+      <sheetName val="QUÂN SỐ"/>
+      <sheetName val="1. QS, TBKT"/>
+      <sheetName val="BaoDamVKTBKT"/>
+      <sheetName val="Đạn"/>
+      <sheetName val="TinhHinhVC"/>
+      <sheetName val="ChiLenhHCKT"/>
+      <sheetName val="PhanCapVCHC"/>
+      <sheetName val="VCHC, VTKT"/>
+      <sheetName val="DuKienKLVatChat"/>
+      <sheetName val="KeHoachVanChuyen"/>
+      <sheetName val="KhoiLuongVanTai"/>
+      <sheetName val="DuKienTiLeTBBB"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4">
+        <row r="6">
+          <cell r="I6" t="e">
+            <v>#REF!</v>
+          </cell>
+          <cell r="R6">
+            <v>1.083</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="I8">
+            <v>1.6</v>
+          </cell>
+          <cell r="R8">
+            <v>1.75</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="I9">
+            <v>1.5</v>
+          </cell>
+          <cell r="R9">
+            <v>1.25</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="I10">
+            <v>0</v>
+          </cell>
+          <cell r="R10">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="I11">
+            <v>1.5</v>
+          </cell>
+          <cell r="R11">
+            <v>1.25</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="I14">
+            <v>0.1</v>
+          </cell>
+          <cell r="R14">
+            <v>0.5</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="R15">
+            <v>0.5</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="I16">
+            <v>1.5</v>
+          </cell>
+          <cell r="R16">
+            <v>1.25</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1520,6 +1789,322 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222B22FA-D9EC-4D91-81DD-ED05F900022D}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="11.26953125" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" customWidth="1"/>
+    <col min="3" max="3" width="13.7265625" customWidth="1"/>
+    <col min="4" max="4" width="13.08984375" customWidth="1"/>
+    <col min="5" max="5" width="12.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="15"/>
+      <c r="B1" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="18">
+      <c r="A2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="21">
+        <f>Sheet4!C10</f>
+        <v>0</v>
+      </c>
+      <c r="C2" s="20">
+        <v>1.4E-2</v>
+      </c>
+      <c r="D2" s="21">
+        <v>24</v>
+      </c>
+      <c r="E2" s="20">
+        <f>B2*C2*D2/1000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="18">
+      <c r="A3" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="21">
+        <f>Sheet4!D10</f>
+        <v>20</v>
+      </c>
+      <c r="C3" s="20">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="D3" s="21">
+        <v>300</v>
+      </c>
+      <c r="E3" s="20">
+        <f>B3*C3*D3/1000</f>
+        <v>0.13199999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="18">
+      <c r="A4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="21">
+        <f>Sheet4!E10</f>
+        <v>3</v>
+      </c>
+      <c r="C4" s="20">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="D4" s="21">
+        <v>600</v>
+      </c>
+      <c r="E4" s="20">
+        <f>B4*C4*D4/1000</f>
+        <v>3.9600000000000003E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18">
+      <c r="A5" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="21">
+        <f>Sheet4!F10</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="20">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="D5" s="21">
+        <v>1200</v>
+      </c>
+      <c r="E5" s="20">
+        <f>B5*C5*D5/1000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="18">
+      <c r="A6" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="21">
+        <f>Sheet4!G10</f>
+        <v>6</v>
+      </c>
+      <c r="C6" s="20">
+        <v>5.5</v>
+      </c>
+      <c r="D6" s="21">
+        <v>12</v>
+      </c>
+      <c r="E6" s="20">
+        <f>B6*C6*D6/1000</f>
+        <v>0.39600000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="17.5">
+      <c r="A7" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="22">
+        <f>SUM(E2:E6)</f>
+        <v>0.56759999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="18">
+      <c r="A8" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="21">
+        <f>Sheet4!I10</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="20">
+        <v>2.1</v>
+      </c>
+      <c r="D8" s="21">
+        <v>80</v>
+      </c>
+      <c r="E8" s="20">
+        <f>D8*C8*B8/1000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="18">
+      <c r="A9" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="21">
+        <f>Sheet4!J10</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="20">
+        <v>5</v>
+      </c>
+      <c r="D9" s="21">
+        <v>100</v>
+      </c>
+      <c r="E9" s="20">
+        <f>D9*C9*B9/1000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="18">
+      <c r="A10" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="21">
+        <f>Sheet4!K10</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="20">
+        <v>23</v>
+      </c>
+      <c r="D10" s="21">
+        <v>80</v>
+      </c>
+      <c r="E10" s="20">
+        <f>D10*C10*B10/1000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="18">
+      <c r="A11" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="21">
+        <f>Sheet4!L10</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="20">
+        <v>16.5</v>
+      </c>
+      <c r="D11" s="21">
+        <v>30</v>
+      </c>
+      <c r="E11" s="20">
+        <f>D11*C11*B11/1000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="17.5">
+      <c r="A12" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="22">
+        <f>SUM(E8:E11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="18">
+      <c r="A13" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="21">
+        <f>Sheet4!M10</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="20">
+        <v>0.17</v>
+      </c>
+      <c r="D13" s="21">
+        <v>1200</v>
+      </c>
+      <c r="E13" s="20">
+        <f>B13*C13*D13/1000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="17.5">
+      <c r="A14" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="24">
+        <f>E13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="18">
+      <c r="A15" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="31">
+        <f>Sheet4!H10</f>
+        <v>102</v>
+      </c>
+      <c r="C15" s="27">
+        <v>0.75</v>
+      </c>
+      <c r="D15" s="28"/>
+      <c r="E15" s="29">
+        <f>C15*B15/1000</f>
+        <v>7.6499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="17.5">
+      <c r="A16" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="24">
+        <f>E15</f>
+        <v>7.6499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="18">
+      <c r="A17" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="31"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="17.5">
+      <c r="A18" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="24">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF17D44A-D0EB-4662-8FA4-7317C80D9FE8}">
   <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -3915,6 +4500,1575 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DFC3E9E-BD01-433A-BDC3-843D19C1F05B}">
+  <dimension ref="A1:AC18"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:29" ht="17.5">
+      <c r="A1" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43" t="s">
+        <v>75</v>
+      </c>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="43"/>
+      <c r="AB1" s="43"/>
+      <c r="AC1" s="43"/>
+    </row>
+    <row r="2" spans="1:29" ht="17.5">
+      <c r="A2" s="43"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" s="45"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="V2" s="45"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="45"/>
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="45"/>
+      <c r="AA2" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB2" s="46"/>
+      <c r="AC2" s="46"/>
+    </row>
+    <row r="3" spans="1:29" ht="17.5">
+      <c r="A3" s="43"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="J3" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="K3" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="M3" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="N3" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="O3" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="P3" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q3" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="R3" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="S3" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="T3" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="U3" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="V3" s="45"/>
+      <c r="W3" s="45"/>
+      <c r="X3" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y3" s="45"/>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="46"/>
+      <c r="AB3" s="46"/>
+      <c r="AC3" s="46"/>
+    </row>
+    <row r="4" spans="1:29" ht="17.5">
+      <c r="A4" s="43"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="J4" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="K4" s="45"/>
+      <c r="L4" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="M4" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="N4" s="45"/>
+      <c r="O4" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="P4" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q4" s="45"/>
+      <c r="R4" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="S4" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="T4" s="45"/>
+      <c r="U4" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="V4" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="W4" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="X4" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y4" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z4" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA4" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB4" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC4" s="47" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="17.5">
+      <c r="A5" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="48" t="e">
+        <f>D6+D7+D12+D18</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="48" t="e">
+        <f>H6+H7+H12+H18</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I5" s="49"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="48" t="e">
+        <f>K6+K7+K12+K18</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L5" s="47"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="48" t="e">
+        <f>N6+N7+N12+N18</f>
+        <v>#REF!</v>
+      </c>
+      <c r="O5" s="47"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="50" t="e">
+        <f>Q6+Q7+Q12+Q18</f>
+        <v>#REF!</v>
+      </c>
+      <c r="R5" s="49"/>
+      <c r="S5" s="47"/>
+      <c r="T5" s="48" t="e">
+        <f>T6+T7+T12+T18</f>
+        <v>#REF!</v>
+      </c>
+      <c r="U5" s="47"/>
+      <c r="V5" s="47"/>
+      <c r="W5" s="48" t="e">
+        <f>W6+W7+W12+W18</f>
+        <v>#REF!</v>
+      </c>
+      <c r="X5" s="47"/>
+      <c r="Y5" s="47"/>
+      <c r="Z5" s="48" t="e">
+        <f>Z6+Z7+Z12+Z18</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AA5" s="47"/>
+      <c r="AB5" s="47"/>
+      <c r="AC5" s="48" t="e">
+        <f>AC6+AC7+AC12+AC18</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="18">
+      <c r="A6" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="51">
+        <f>AF6</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D6" s="53" t="e">
+        <f>C6*AI6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H6" s="53" t="e">
+        <f>G6*AI6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I6" s="54">
+        <v>0.3</v>
+      </c>
+      <c r="J6" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!I6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K6" s="53" t="e">
+        <f>(I6+J6)*AI6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L6" s="52" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M6" s="54"/>
+      <c r="N6" s="53" t="e">
+        <f>L6*AO6+M6*AU6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="O6" s="52" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P6" s="54"/>
+      <c r="Q6" s="55" t="e">
+        <f>O6*AO6+P6*AU6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="R6" s="54">
+        <v>1.75</v>
+      </c>
+      <c r="S6" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!R6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="T6" s="53" t="e">
+        <f>(R6+S6)*AI6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="U6" s="52" t="e">
+        <f>E6+R6-L6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="V6" s="52">
+        <f>E6+R6-M6</f>
+        <v>1.75</v>
+      </c>
+      <c r="W6" s="53" t="e">
+        <f>U6*AO6+V6*AU6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="X6" s="52" t="e">
+        <f>E6+S6-O6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Y6" s="52" t="e">
+        <f>E6+S6-P6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Z6" s="53" t="e">
+        <f>X6*AO6+Y6*AU6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AA6" s="52" t="e">
+        <f>G6+I6-R6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AB6" s="52" t="e">
+        <f>J6-S6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AC6" s="53" t="e">
+        <f>(AA6+AB6)*AI6</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="18">
+      <c r="A7" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="51"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="48" t="e">
+        <f>D8+D9+D10+D11</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="48" t="e">
+        <f>H8+H9+H10+H11</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I7" s="49"/>
+      <c r="J7" s="47"/>
+      <c r="K7" s="48" t="e">
+        <f>K8+K9+K10+K11</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L7" s="47"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="48" t="e">
+        <f>N8+N9+N10+N11</f>
+        <v>#REF!</v>
+      </c>
+      <c r="O7" s="47"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="50" t="e">
+        <f>Q8+Q9+Q10+Q11</f>
+        <v>#REF!</v>
+      </c>
+      <c r="R7" s="49"/>
+      <c r="S7" s="47"/>
+      <c r="T7" s="48" t="e">
+        <f>T8+T9+T10+T11</f>
+        <v>#REF!</v>
+      </c>
+      <c r="U7" s="47"/>
+      <c r="V7" s="47"/>
+      <c r="W7" s="48" t="e">
+        <f>W8+W9+W10+W11</f>
+        <v>#REF!</v>
+      </c>
+      <c r="X7" s="47"/>
+      <c r="Y7" s="47"/>
+      <c r="Z7" s="48" t="e">
+        <f>Z8+Z9+Z10+Z11</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AA7" s="47"/>
+      <c r="AB7" s="47"/>
+      <c r="AC7" s="48" t="e">
+        <f>AC8+AC9+AC10+AC11</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="18">
+      <c r="A8" s="52" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="51">
+        <f t="shared" ref="B8:B18" si="0">AF8</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D8" s="53" t="e">
+        <f>C8*AI8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H8" s="53" t="e">
+        <f t="shared" ref="H8:H18" si="1">G8*AI8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I8" s="54">
+        <v>0.1</v>
+      </c>
+      <c r="J8" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!I8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K8" s="53" t="e">
+        <f t="shared" ref="K8:K18" si="2">(I8+J8)*AI8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L8" s="52" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M8" s="54"/>
+      <c r="N8" s="53" t="e">
+        <f t="shared" ref="N8:N18" si="3">L8*AO8+M8*AU8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="O8" s="52" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P8" s="54"/>
+      <c r="Q8" s="55" t="e">
+        <f t="shared" ref="Q8:Q18" si="4">O8*AO8+P8*AU8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="R8" s="54">
+        <v>1</v>
+      </c>
+      <c r="S8" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!R8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="T8" s="53" t="e">
+        <f t="shared" ref="T8:T18" si="5">(R8+S8)*AI8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="U8" s="52" t="e">
+        <f>E8+R8-L8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="V8" s="52">
+        <f>E8+R8-M8</f>
+        <v>1</v>
+      </c>
+      <c r="W8" s="53" t="e">
+        <f t="shared" ref="W8:W18" si="6">U8*AO8+V8*AU8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="X8" s="52" t="e">
+        <f>E8+S8-O8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Y8" s="52" t="e">
+        <f>E8+S8-P8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Z8" s="53" t="e">
+        <f t="shared" ref="Z8:Z18" si="7">X8*AO8+Y8*AU8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AA8" s="52" t="e">
+        <f>G8+I8-R8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AB8" s="52" t="e">
+        <f>J8-S8</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AC8" s="53" t="e">
+        <f t="shared" ref="AC8:AC18" si="8">(AA8+AB8)*AI8</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="36">
+      <c r="A9" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C9" s="56" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D9" s="53" t="e">
+        <f t="shared" ref="D9:D18" si="9">C9*AI9</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H9" s="53" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I9" s="54">
+        <v>0.1</v>
+      </c>
+      <c r="J9" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!I9</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K9" s="53" t="e">
+        <f t="shared" si="2"/>
+        <v>#REF!</v>
+      </c>
+      <c r="L9" s="52" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M9" s="54"/>
+      <c r="N9" s="53" t="e">
+        <f t="shared" si="3"/>
+        <v>#REF!</v>
+      </c>
+      <c r="O9" s="52" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P9" s="54"/>
+      <c r="Q9" s="55" t="e">
+        <f t="shared" si="4"/>
+        <v>#REF!</v>
+      </c>
+      <c r="R9" s="54">
+        <v>1</v>
+      </c>
+      <c r="S9" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!R9</f>
+        <v>#REF!</v>
+      </c>
+      <c r="T9" s="53" t="e">
+        <f t="shared" si="5"/>
+        <v>#REF!</v>
+      </c>
+      <c r="U9" s="52" t="e">
+        <f t="shared" ref="U9:U11" si="10">E9+R9-L9</f>
+        <v>#REF!</v>
+      </c>
+      <c r="V9" s="52">
+        <f t="shared" ref="V9:V11" si="11">E9+R9-M9</f>
+        <v>1</v>
+      </c>
+      <c r="W9" s="53" t="e">
+        <f t="shared" si="6"/>
+        <v>#REF!</v>
+      </c>
+      <c r="X9" s="52" t="e">
+        <f t="shared" ref="X9:X11" si="12">E9+S9-O9</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Y9" s="52" t="e">
+        <f t="shared" ref="Y9:Y18" si="13">E9+S9-P9</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Z9" s="53" t="e">
+        <f t="shared" si="7"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AA9" s="52" t="e">
+        <f t="shared" ref="AA9:AA18" si="14">G9+I9-R9</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AB9" s="52" t="e">
+        <f t="shared" ref="AB9:AB11" si="15">J9-S9</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AC9" s="53" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="36">
+      <c r="A10" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C10" s="56" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D10" s="53" t="e">
+        <f t="shared" si="9"/>
+        <v>#REF!</v>
+      </c>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H10" s="53" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I10" s="54">
+        <v>0.1</v>
+      </c>
+      <c r="J10" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!I10</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K10" s="53" t="e">
+        <f>(I10+J10)*AI10</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L10" s="52" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M10" s="54"/>
+      <c r="N10" s="53" t="e">
+        <f t="shared" si="3"/>
+        <v>#REF!</v>
+      </c>
+      <c r="O10" s="52" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="55" t="e">
+        <f t="shared" si="4"/>
+        <v>#REF!</v>
+      </c>
+      <c r="R10" s="54">
+        <v>1</v>
+      </c>
+      <c r="S10" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!R10</f>
+        <v>#REF!</v>
+      </c>
+      <c r="T10" s="53" t="e">
+        <f t="shared" si="5"/>
+        <v>#REF!</v>
+      </c>
+      <c r="U10" s="52" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
+      </c>
+      <c r="V10" s="52">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="W10" s="53" t="e">
+        <f t="shared" si="6"/>
+        <v>#REF!</v>
+      </c>
+      <c r="X10" s="52" t="e">
+        <f t="shared" si="12"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Y10" s="52" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Z10" s="53" t="e">
+        <f>X10*AO10+Y10*AU10</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AA10" s="52" t="e">
+        <f t="shared" si="14"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AB10" s="52" t="e">
+        <f t="shared" si="15"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AC10" s="53" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="36">
+      <c r="A11" s="56" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C11" s="56" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D11" s="53" t="e">
+        <f t="shared" si="9"/>
+        <v>#REF!</v>
+      </c>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H11" s="53" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I11" s="54">
+        <v>0.2</v>
+      </c>
+      <c r="J11" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!I11</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K11" s="53" t="e">
+        <f>(I11+J11)*AI11</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L11" s="52" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M11" s="54"/>
+      <c r="N11" s="53" t="e">
+        <f t="shared" si="3"/>
+        <v>#REF!</v>
+      </c>
+      <c r="O11" s="52" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="55" t="e">
+        <f t="shared" si="4"/>
+        <v>#REF!</v>
+      </c>
+      <c r="R11" s="54">
+        <v>1</v>
+      </c>
+      <c r="S11" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!R11</f>
+        <v>#REF!</v>
+      </c>
+      <c r="T11" s="53" t="e">
+        <f t="shared" si="5"/>
+        <v>#REF!</v>
+      </c>
+      <c r="U11" s="52" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
+      </c>
+      <c r="V11" s="52">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="W11" s="53" t="e">
+        <f t="shared" si="6"/>
+        <v>#REF!</v>
+      </c>
+      <c r="X11" s="52" t="e">
+        <f t="shared" si="12"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Y11" s="52" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Z11" s="53" t="e">
+        <f t="shared" si="7"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AA11" s="52" t="e">
+        <f t="shared" si="14"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AB11" s="52" t="e">
+        <f t="shared" si="15"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AC11" s="53" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="70">
+      <c r="A12" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="51"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="48" t="e">
+        <f>D13+D14+D15+D16+D17</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="48" t="e">
+        <f>H13+H14+H15+H16+H17</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I12" s="49"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="48" t="e">
+        <f>K13+K14+K15+K16+K17</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L12" s="47"/>
+      <c r="M12" s="49"/>
+      <c r="N12" s="48" t="e">
+        <f>N13+N14+N15+N16+N17</f>
+        <v>#REF!</v>
+      </c>
+      <c r="O12" s="47"/>
+      <c r="P12" s="49"/>
+      <c r="Q12" s="50" t="e">
+        <f>Q13+Q14+Q15+Q16+Q17</f>
+        <v>#REF!</v>
+      </c>
+      <c r="R12" s="49"/>
+      <c r="S12" s="47"/>
+      <c r="T12" s="48" t="e">
+        <f>T13+T14+T15+T16+T17</f>
+        <v>#REF!</v>
+      </c>
+      <c r="U12" s="57"/>
+      <c r="V12" s="57"/>
+      <c r="W12" s="48" t="e">
+        <f>W13+W14+W15+W16+W17</f>
+        <v>#REF!</v>
+      </c>
+      <c r="X12" s="47"/>
+      <c r="Y12" s="47"/>
+      <c r="Z12" s="48" t="e">
+        <f>Z13+Z14+Z15+Z16+Z17</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AA12" s="47"/>
+      <c r="AB12" s="47"/>
+      <c r="AC12" s="48" t="e">
+        <f>AC13+AC14+AC15+AC16+AC17</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="36">
+      <c r="A13" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C13" s="56" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D13" s="53" t="e">
+        <f t="shared" si="9"/>
+        <v>#REF!</v>
+      </c>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="56" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H13" s="53" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I13" s="58">
+        <v>0.33</v>
+      </c>
+      <c r="J13" s="56" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!I13</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K13" s="53" t="e">
+        <f t="shared" si="2"/>
+        <v>#REF!</v>
+      </c>
+      <c r="L13" s="56" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M13" s="58"/>
+      <c r="N13" s="53" t="e">
+        <f t="shared" si="3"/>
+        <v>#REF!</v>
+      </c>
+      <c r="O13" s="56" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P13" s="58"/>
+      <c r="Q13" s="55" t="e">
+        <f t="shared" si="4"/>
+        <v>#REF!</v>
+      </c>
+      <c r="R13" s="58">
+        <v>1.25</v>
+      </c>
+      <c r="S13" s="56" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!R13</f>
+        <v>#REF!</v>
+      </c>
+      <c r="T13" s="53" t="e">
+        <f t="shared" si="5"/>
+        <v>#REF!</v>
+      </c>
+      <c r="U13" s="52" t="e">
+        <f>E13+R13-L13</f>
+        <v>#REF!</v>
+      </c>
+      <c r="V13" s="52">
+        <f>E13+R13-M13</f>
+        <v>1.25</v>
+      </c>
+      <c r="W13" s="53" t="e">
+        <f t="shared" si="6"/>
+        <v>#REF!</v>
+      </c>
+      <c r="X13" s="52" t="e">
+        <f>E13+S13-O13</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Y13" s="52" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Z13" s="53" t="e">
+        <f t="shared" si="7"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AA13" s="52" t="e">
+        <f t="shared" si="14"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AB13" s="52" t="e">
+        <f>J13-S13</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AC13" s="53" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="36">
+      <c r="A14" s="56" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C14" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D14" s="53" t="e">
+        <f t="shared" si="9"/>
+        <v>#REF!</v>
+      </c>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="56" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H14" s="53" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I14" s="58">
+        <v>0.5</v>
+      </c>
+      <c r="J14" s="56" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!I14</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K14" s="53" t="e">
+        <f t="shared" si="2"/>
+        <v>#REF!</v>
+      </c>
+      <c r="L14" s="56" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M14" s="58"/>
+      <c r="N14" s="53" t="e">
+        <f t="shared" si="3"/>
+        <v>#REF!</v>
+      </c>
+      <c r="O14" s="56" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P14" s="58"/>
+      <c r="Q14" s="55" t="e">
+        <f t="shared" si="4"/>
+        <v>#REF!</v>
+      </c>
+      <c r="R14" s="58">
+        <v>1.25</v>
+      </c>
+      <c r="S14" s="56" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!R14</f>
+        <v>#REF!</v>
+      </c>
+      <c r="T14" s="53" t="e">
+        <f t="shared" si="5"/>
+        <v>#REF!</v>
+      </c>
+      <c r="U14" s="52" t="e">
+        <f t="shared" ref="U14:U18" si="16">E14+R14-L14</f>
+        <v>#REF!</v>
+      </c>
+      <c r="V14" s="52">
+        <f t="shared" ref="V14:V18" si="17">E14+R14-M14</f>
+        <v>1.25</v>
+      </c>
+      <c r="W14" s="53" t="e">
+        <f t="shared" si="6"/>
+        <v>#REF!</v>
+      </c>
+      <c r="X14" s="52" t="e">
+        <f t="shared" ref="X14:X18" si="18">E14+S14-O14</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Y14" s="52" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Z14" s="53" t="e">
+        <f t="shared" si="7"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AA14" s="52" t="e">
+        <f t="shared" si="14"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AB14" s="52" t="e">
+        <f t="shared" ref="AB14:AB18" si="19">J14-S14</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AC14" s="53" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="54">
+      <c r="A15" s="56" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C15" s="56" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D15" s="53" t="e">
+        <f t="shared" si="9"/>
+        <v>#REF!</v>
+      </c>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="56" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H15" s="53" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I15" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="J15" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!I15</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K15" s="53" t="e">
+        <f t="shared" si="2"/>
+        <v>#REF!</v>
+      </c>
+      <c r="L15" s="56" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M15" s="58"/>
+      <c r="N15" s="53" t="e">
+        <f t="shared" si="3"/>
+        <v>#REF!</v>
+      </c>
+      <c r="O15" s="56" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P15" s="58"/>
+      <c r="Q15" s="55" t="e">
+        <f t="shared" si="4"/>
+        <v>#REF!</v>
+      </c>
+      <c r="R15" s="58">
+        <v>1.25</v>
+      </c>
+      <c r="S15" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!R15</f>
+        <v>#REF!</v>
+      </c>
+      <c r="T15" s="53" t="e">
+        <f t="shared" si="5"/>
+        <v>#REF!</v>
+      </c>
+      <c r="U15" s="52" t="e">
+        <f t="shared" si="16"/>
+        <v>#REF!</v>
+      </c>
+      <c r="V15" s="52">
+        <f t="shared" si="17"/>
+        <v>1.25</v>
+      </c>
+      <c r="W15" s="53" t="e">
+        <f t="shared" si="6"/>
+        <v>#REF!</v>
+      </c>
+      <c r="X15" s="52" t="e">
+        <f t="shared" si="18"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Y15" s="52" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Z15" s="53" t="e">
+        <f t="shared" si="7"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AA15" s="52" t="e">
+        <f t="shared" si="14"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AB15" s="52" t="e">
+        <f t="shared" si="19"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AC15" s="53" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="54">
+      <c r="A16" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C16" s="56" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D16" s="53" t="e">
+        <f t="shared" si="9"/>
+        <v>#REF!</v>
+      </c>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="56" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H16" s="53" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I16" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="J16" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!I16</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K16" s="53" t="e">
+        <f t="shared" si="2"/>
+        <v>#REF!</v>
+      </c>
+      <c r="L16" s="56" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M16" s="58"/>
+      <c r="N16" s="53" t="e">
+        <f t="shared" si="3"/>
+        <v>#REF!</v>
+      </c>
+      <c r="O16" s="56" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P16" s="58"/>
+      <c r="Q16" s="55" t="e">
+        <f t="shared" si="4"/>
+        <v>#REF!</v>
+      </c>
+      <c r="R16" s="58">
+        <v>1.25</v>
+      </c>
+      <c r="S16" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!R16</f>
+        <v>#REF!</v>
+      </c>
+      <c r="T16" s="53" t="e">
+        <f t="shared" si="5"/>
+        <v>#REF!</v>
+      </c>
+      <c r="U16" s="52" t="e">
+        <f t="shared" si="16"/>
+        <v>#REF!</v>
+      </c>
+      <c r="V16" s="52">
+        <f t="shared" si="17"/>
+        <v>1.25</v>
+      </c>
+      <c r="W16" s="53" t="e">
+        <f t="shared" si="6"/>
+        <v>#REF!</v>
+      </c>
+      <c r="X16" s="52" t="e">
+        <f t="shared" si="18"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Y16" s="52" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Z16" s="53" t="e">
+        <f>X16*AO16+Y16*AU16</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AA16" s="52" t="e">
+        <f t="shared" si="14"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AB16" s="52" t="e">
+        <f t="shared" si="19"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AC16" s="53" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" ht="36">
+      <c r="A17" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C17" s="56" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D17" s="53" t="e">
+        <f t="shared" si="9"/>
+        <v>#REF!</v>
+      </c>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="56" t="e">
+        <f>[1]ChiLenhHCKT!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H17" s="53" t="e">
+        <f t="shared" si="1"/>
+        <v>#REF!</v>
+      </c>
+      <c r="I17" s="54">
+        <v>1</v>
+      </c>
+      <c r="J17" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!I17</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K17" s="53" t="e">
+        <f t="shared" si="2"/>
+        <v>#REF!</v>
+      </c>
+      <c r="L17" s="56" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M17" s="58"/>
+      <c r="N17" s="53" t="e">
+        <f t="shared" si="3"/>
+        <v>#REF!</v>
+      </c>
+      <c r="O17" s="56" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P17" s="58"/>
+      <c r="Q17" s="55" t="e">
+        <f t="shared" si="4"/>
+        <v>#REF!</v>
+      </c>
+      <c r="R17" s="58">
+        <v>1.25</v>
+      </c>
+      <c r="S17" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!R17</f>
+        <v>#REF!</v>
+      </c>
+      <c r="T17" s="53" t="e">
+        <f t="shared" si="5"/>
+        <v>#REF!</v>
+      </c>
+      <c r="U17" s="52" t="e">
+        <f t="shared" si="16"/>
+        <v>#REF!</v>
+      </c>
+      <c r="V17" s="52">
+        <f t="shared" si="17"/>
+        <v>1.25</v>
+      </c>
+      <c r="W17" s="53" t="e">
+        <f t="shared" si="6"/>
+        <v>#REF!</v>
+      </c>
+      <c r="X17" s="52" t="e">
+        <f t="shared" si="18"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Y17" s="52" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Z17" s="53" t="e">
+        <f t="shared" si="7"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AA17" s="52" t="e">
+        <f t="shared" si="14"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AB17" s="52" t="e">
+        <f t="shared" si="19"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AC17" s="53" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" ht="35">
+      <c r="A18" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C18" s="56">
+        <v>1.2</v>
+      </c>
+      <c r="D18" s="48">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="56">
+        <v>0.75</v>
+      </c>
+      <c r="H18" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="54">
+        <v>0.2</v>
+      </c>
+      <c r="J18" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!I18</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K18" s="48" t="e">
+        <f t="shared" si="2"/>
+        <v>#REF!</v>
+      </c>
+      <c r="L18" s="56" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M18" s="58"/>
+      <c r="N18" s="48" t="e">
+        <f t="shared" si="3"/>
+        <v>#REF!</v>
+      </c>
+      <c r="O18" s="56" t="e">
+        <f>[1]TinhHinhVC!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P18" s="58"/>
+      <c r="Q18" s="50" t="e">
+        <f t="shared" si="4"/>
+        <v>#REF!</v>
+      </c>
+      <c r="R18" s="58">
+        <v>1.25</v>
+      </c>
+      <c r="S18" s="52" t="e">
+        <f>[1]ChiLenhHCKT!#REF!-[1]Đạn!R18</f>
+        <v>#REF!</v>
+      </c>
+      <c r="T18" s="48" t="e">
+        <f t="shared" si="5"/>
+        <v>#REF!</v>
+      </c>
+      <c r="U18" s="52" t="e">
+        <f t="shared" si="16"/>
+        <v>#REF!</v>
+      </c>
+      <c r="V18" s="52">
+        <f t="shared" si="17"/>
+        <v>1.25</v>
+      </c>
+      <c r="W18" s="48" t="e">
+        <f>U18*AO18+V18*AU18</f>
+        <v>#REF!</v>
+      </c>
+      <c r="X18" s="52" t="e">
+        <f t="shared" si="18"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Y18" s="52" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
+      </c>
+      <c r="Z18" s="48" t="e">
+        <f t="shared" si="7"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AA18" s="52">
+        <f t="shared" si="14"/>
+        <v>-0.30000000000000004</v>
+      </c>
+      <c r="AB18" s="52" t="e">
+        <f t="shared" si="19"/>
+        <v>#REF!</v>
+      </c>
+      <c r="AC18" s="48" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="U3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="R1:T2"/>
+    <mergeCell ref="U1:AC1"/>
+    <mergeCell ref="E2:F3"/>
+    <mergeCell ref="G2:H3"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="U2:Z2"/>
+    <mergeCell ref="AA2:AC3"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="I1:K2"/>
+    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="Q3:Q4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E752DEA2-144B-449F-BE2E-E569AC4C7928}">
   <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -4229,7 +6383,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E25128-12AB-402D-BBD3-AD3795682E35}">
   <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -4544,7 +6698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E76C6BE-B739-4E04-B0A6-9776C2F546D5}">
   <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -4857,320 +7011,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222B22FA-D9EC-4D91-81DD-ED05F900022D}">
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="11.26953125" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" customWidth="1"/>
-    <col min="3" max="3" width="13.7265625" customWidth="1"/>
-    <col min="4" max="4" width="13.08984375" customWidth="1"/>
-    <col min="5" max="5" width="12.6328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="15"/>
-      <c r="B1" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="18">
-      <c r="A2" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="21">
-        <f>Sheet4!C10</f>
-        <v>0</v>
-      </c>
-      <c r="C2" s="20">
-        <v>1.4E-2</v>
-      </c>
-      <c r="D2" s="21">
-        <v>24</v>
-      </c>
-      <c r="E2" s="20">
-        <f>B2*C2*D2/1000</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="18">
-      <c r="A3" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="21">
-        <f>Sheet4!D10</f>
-        <v>20</v>
-      </c>
-      <c r="C3" s="20">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="D3" s="21">
-        <v>300</v>
-      </c>
-      <c r="E3" s="20">
-        <f>B3*C3*D3/1000</f>
-        <v>0.13199999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="18">
-      <c r="A4" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="21">
-        <f>Sheet4!E10</f>
-        <v>3</v>
-      </c>
-      <c r="C4" s="20">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="D4" s="21">
-        <v>600</v>
-      </c>
-      <c r="E4" s="20">
-        <f>B4*C4*D4/1000</f>
-        <v>3.9600000000000003E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="18">
-      <c r="A5" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="21">
-        <f>Sheet4!F10</f>
-        <v>0</v>
-      </c>
-      <c r="C5" s="20">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="D5" s="21">
-        <v>1200</v>
-      </c>
-      <c r="E5" s="20">
-        <f>B5*C5*D5/1000</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="18">
-      <c r="A6" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="21">
-        <f>Sheet4!G10</f>
-        <v>6</v>
-      </c>
-      <c r="C6" s="20">
-        <v>5.5</v>
-      </c>
-      <c r="D6" s="21">
-        <v>12</v>
-      </c>
-      <c r="E6" s="20">
-        <f>B6*C6*D6/1000</f>
-        <v>0.39600000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="17.5">
-      <c r="A7" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="22">
-        <f>SUM(E2:E6)</f>
-        <v>0.56759999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="18">
-      <c r="A8" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="21">
-        <f>Sheet4!I10</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="20">
-        <v>2.1</v>
-      </c>
-      <c r="D8" s="21">
-        <v>80</v>
-      </c>
-      <c r="E8" s="20">
-        <f>D8*C8*B8/1000</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="18">
-      <c r="A9" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="21">
-        <f>Sheet4!J10</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="20">
-        <v>5</v>
-      </c>
-      <c r="D9" s="21">
-        <v>100</v>
-      </c>
-      <c r="E9" s="20">
-        <f>D9*C9*B9/1000</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="18">
-      <c r="A10" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="21">
-        <f>Sheet4!K10</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="20">
-        <v>23</v>
-      </c>
-      <c r="D10" s="21">
-        <v>80</v>
-      </c>
-      <c r="E10" s="20">
-        <f>D10*C10*B10/1000</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="18">
-      <c r="A11" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="21">
-        <f>Sheet4!L10</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="20">
-        <v>16.5</v>
-      </c>
-      <c r="D11" s="21">
-        <v>30</v>
-      </c>
-      <c r="E11" s="20">
-        <f>D11*C11*B11/1000</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="17.5">
-      <c r="A12" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="22">
-        <f>SUM(E8:E11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="18">
-      <c r="A13" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="21">
-        <f>Sheet4!M10</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="20">
-        <v>0.17</v>
-      </c>
-      <c r="D13" s="21">
-        <v>1200</v>
-      </c>
-      <c r="E13" s="20">
-        <f>B13*C13*D13/1000</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="17.5">
-      <c r="A14" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="24">
-        <f>E13</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="18">
-      <c r="A15" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="31">
-        <f>Sheet4!H10</f>
-        <v>102</v>
-      </c>
-      <c r="C15" s="27">
-        <v>0.75</v>
-      </c>
-      <c r="D15" s="28"/>
-      <c r="E15" s="29">
-        <f>C15*B15/1000</f>
-        <v>7.6499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="17.5">
-      <c r="A16" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="24">
-        <f>E15</f>
-        <v>7.6499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="18">
-      <c r="A17" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="31"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="17.5">
-      <c r="A18" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="24">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>